--- a/src/assets/Decision template.xlsx
+++ b/src/assets/Decision template.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Decision" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Factors" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Options" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t xml:space="preserve">Decision:</t>
   </si>
@@ -84,6 +85,12 @@
   </si>
   <si>
     <t xml:space="preserve">Max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
   </si>
 </sst>
 </file>
@@ -195,37 +202,45 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -481,50 +496,50 @@
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="2" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="21.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0"/>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -572,54 +587,54 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="12.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -632,4 +647,60 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="34.37"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/assets/Decision template.xlsx
+++ b/src/assets/Decision template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Decision" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t xml:space="preserve">Decision:</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden</t>
   </si>
 </sst>
 </file>
@@ -202,7 +205,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -239,8 +242,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -654,19 +661,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="19.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="34.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>22</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/src/assets/Decision template.xlsx
+++ b/src/assets/Decision template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Decision" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
   <si>
     <t xml:space="preserve">Decision:</t>
   </si>
@@ -33,10 +33,13 @@
     <t xml:space="preserve">Factors must be in column A, starting from A6. The factors here must also be listed in the “Factors” sheet (even if they’re empty)</t>
   </si>
   <si>
+    <t xml:space="preserve">Options must be on line 5 starting from B5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Options</t>
   </si>
   <si>
-    <t xml:space="preserve">Options must be on line 5 starting from B5</t>
+    <t xml:space="preserve">Answers can be any one of the following: a number (within the appropriate range for the factor), a range (i.e. 4-5, but be careful not to let your program format it as a date), or a label (for discrete factors only, see the factors page)</t>
   </si>
   <si>
     <t xml:space="preserve">Factors</t>
@@ -87,6 +90,16 @@
     <t xml:space="preserve">Max</t>
   </si>
   <si>
+    <t xml:space="preserve">Define the details of the factors here (or leave empty to add them in the site)
+The canonical colors are pulled from here (and Options), not the Decision tab.
+Unit can be anything, but if it follows this format:
+0: Option, 1: Other option, 2: etc
+Then that defines a “discrete” factor that you can set in the Decision page by putting
+label down instead of a number.
+Remember that discrete factors need to make sense! (i.e. “1: tacos, 2: burritos” doesn’t
+make sense, but “1: Small, 2: Medium, 3: Large” does make sense)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Option</t>
   </si>
   <si>
@@ -94,6 +107,10 @@
   </si>
   <si>
     <t xml:space="preserve">Hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here you can add optional notes. These colors are definitive, not the ones
+in the Decision tab.</t>
   </si>
 </sst>
 </file>
@@ -102,14 +119,13 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -128,29 +144,53 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF729FCF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF81ACA6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEEFF"/>
+        <bgColor rgb="FFD8F3EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3BF"/>
+        <bgColor rgb="FFFCE8D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE8D5"/>
+        <bgColor rgb="FFFFF3BF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8F3EA"/>
+        <bgColor rgb="FFDDEEFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -165,20 +205,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -205,20 +231,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -226,27 +252,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -262,7 +300,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFCE8D5"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -279,8 +317,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFF3BF"/>
+      <rgbColor rgb="FFD8F3EA"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -294,7 +332,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFDDEEFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -308,7 +346,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF81ACA6"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -499,15 +537,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="2" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="21.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,66 +553,101 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="D5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -591,60 +664,92 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="12.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="132.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="H2" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
+        <v>10</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -661,56 +766,78 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="19.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="34.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="10" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="11"/>
+      <c r="E2" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
+      <c r="B5" s="2"/>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>